--- a/table/resources/sample/common/RobotAction_Bet.xlsx
+++ b/table/resources/sample/common/RobotAction_Bet.xlsx
@@ -178,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="54">
   <si>
     <t>序列</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>龙虎斗高级场</t>
+  </si>
+  <si>
+    <t>小额下注1</t>
   </si>
 </sst>
 </file>
@@ -4019,7 +4022,7 @@
         <v>10001</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D79" s="5">
         <v>2001013</v>

--- a/table/resources/sample/common/RobotAction_Bet.xlsx
+++ b/table/resources/sample/common/RobotAction_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BetRobot" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="53">
   <si>
     <t>序列</t>
   </si>
@@ -213,7 +213,7 @@
     <t>list&lt;list&lt;int&gt;{,2}&gt;{;}</t>
   </si>
   <si>
-    <t>id</t>
+    <t>ID</t>
   </si>
   <si>
     <t>ActionID</t>
@@ -337,9 +337,6 @@
   </si>
   <si>
     <t>龙虎斗高级场</t>
-  </si>
-  <si>
-    <t>小额下注1</t>
   </si>
 </sst>
 </file>
@@ -4022,7 +4019,7 @@
         <v>10001</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D79" s="5">
         <v>2001013</v>

--- a/table/resources/sample/common/RobotAction_Bet.xlsx
+++ b/table/resources/sample/common/RobotAction_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BetRobot" sheetId="1" r:id="rId1"/>

--- a/table/resources/sample/common/RobotAction_Bet.xlsx
+++ b/table/resources/sample/common/RobotAction_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BetRobot" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="69">
   <si>
     <t>序列</t>
   </si>
@@ -337,6 +337,54 @@
   </si>
   <si>
     <t>龙虎斗高级场</t>
+  </si>
+  <si>
+    <t>三个骰子基础场</t>
+  </si>
+  <si>
+    <t>41,20060001;41,20060002;41,20060003;244,20060004;41,20060005;41,20060006;41,20060007;1098,20060008;41,20060009;81,20060010;122,20060011;163,20060012;203,20060013;244,20060014;244,20060015;244,20060016;244,20060017;203,20060018;163,20060019;122,20060020;81,20060021;41,20060022;854,20060023;854,20060024;854,20060025;854,20060026;854,20060027;854,20060028;1098,20060029</t>
+  </si>
+  <si>
+    <t>三个骰子中级场</t>
+  </si>
+  <si>
+    <t>三个骰子高级场</t>
+  </si>
+  <si>
+    <t>色碟基础场</t>
+  </si>
+  <si>
+    <t>1111,20070001;1111,20070002;3333,20070003;2222,20070004;1111,20070005;1111,20070006</t>
+  </si>
+  <si>
+    <t>色碟中级场</t>
+  </si>
+  <si>
+    <t>色碟高级场</t>
+  </si>
+  <si>
+    <t>大小骰子基础场</t>
+  </si>
+  <si>
+    <t>5000,20080001;5000,20080002</t>
+  </si>
+  <si>
+    <t>大小骰子中级场</t>
+  </si>
+  <si>
+    <t>大小骰子高级场</t>
+  </si>
+  <si>
+    <t>鱼虾蟹基础场</t>
+  </si>
+  <si>
+    <t>1667,20090001;1667,20090002;1667,20090003;1667,20090004;1667,20090005;1667,20090006</t>
+  </si>
+  <si>
+    <t>鱼虾蟹中级场</t>
+  </si>
+  <si>
+    <t>鱼虾蟹高级场</t>
   </si>
 </sst>
 </file>
@@ -513,18 +561,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -546,6 +594,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -866,7 +938,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -890,16 +962,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -908,25 +980,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -989,8 +1049,20 @@
     <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1014,6 +1086,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1541,7 +1625,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="4" width="12.875" style="1" customWidth="1"/>
@@ -4043,6 +4127,1926 @@
         <v>32</v>
       </c>
     </row>
+    <row r="80" spans="1:10">
+      <c r="A80">
+        <v>76</v>
+      </c>
+      <c r="B80" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80" s="5">
+        <v>2006001</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F80">
+        <v>9000</v>
+      </c>
+      <c r="G80" t="s">
+        <v>21</v>
+      </c>
+      <c r="H80" t="s">
+        <v>54</v>
+      </c>
+      <c r="I80" t="s">
+        <v>23</v>
+      </c>
+      <c r="J80" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81">
+        <v>77</v>
+      </c>
+      <c r="B81" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" s="5">
+        <v>2006002</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F81">
+        <v>9000</v>
+      </c>
+      <c r="G81" t="s">
+        <v>21</v>
+      </c>
+      <c r="H81" t="s">
+        <v>54</v>
+      </c>
+      <c r="I81" t="s">
+        <v>23</v>
+      </c>
+      <c r="J81" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82">
+        <v>78</v>
+      </c>
+      <c r="B82" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="5">
+        <v>2006003</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F82">
+        <v>9000</v>
+      </c>
+      <c r="G82" t="s">
+        <v>21</v>
+      </c>
+      <c r="H82" t="s">
+        <v>54</v>
+      </c>
+      <c r="I82" t="s">
+        <v>23</v>
+      </c>
+      <c r="J82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83">
+        <v>79</v>
+      </c>
+      <c r="B83" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="5">
+        <v>2006001</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F83">
+        <v>7000</v>
+      </c>
+      <c r="G83" t="s">
+        <v>28</v>
+      </c>
+      <c r="H83" t="s">
+        <v>54</v>
+      </c>
+      <c r="I83" t="s">
+        <v>23</v>
+      </c>
+      <c r="J83" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84">
+        <v>80</v>
+      </c>
+      <c r="B84" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D84" s="5">
+        <v>2006002</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F84">
+        <v>7000</v>
+      </c>
+      <c r="G84" t="s">
+        <v>28</v>
+      </c>
+      <c r="H84" t="s">
+        <v>54</v>
+      </c>
+      <c r="I84" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85">
+        <v>81</v>
+      </c>
+      <c r="B85" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" s="5">
+        <v>2006003</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F85">
+        <v>7000</v>
+      </c>
+      <c r="G85" t="s">
+        <v>28</v>
+      </c>
+      <c r="H85" t="s">
+        <v>54</v>
+      </c>
+      <c r="I85" t="s">
+        <v>23</v>
+      </c>
+      <c r="J85" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86">
+        <v>82</v>
+      </c>
+      <c r="B86" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="5">
+        <v>2006001</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F86">
+        <v>5000</v>
+      </c>
+      <c r="G86" t="s">
+        <v>31</v>
+      </c>
+      <c r="H86" t="s">
+        <v>54</v>
+      </c>
+      <c r="I86" t="s">
+        <v>23</v>
+      </c>
+      <c r="J86" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87">
+        <v>83</v>
+      </c>
+      <c r="B87" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D87" s="5">
+        <v>2006002</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F87">
+        <v>5000</v>
+      </c>
+      <c r="G87" t="s">
+        <v>31</v>
+      </c>
+      <c r="H87" t="s">
+        <v>54</v>
+      </c>
+      <c r="I87" t="s">
+        <v>23</v>
+      </c>
+      <c r="J87" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88">
+        <v>84</v>
+      </c>
+      <c r="B88" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D88" s="5">
+        <v>2006003</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F88">
+        <v>5000</v>
+      </c>
+      <c r="G88" t="s">
+        <v>31</v>
+      </c>
+      <c r="H88" t="s">
+        <v>54</v>
+      </c>
+      <c r="I88" t="s">
+        <v>23</v>
+      </c>
+      <c r="J88" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89">
+        <v>85</v>
+      </c>
+      <c r="B89" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="5">
+        <v>2006001</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F89">
+        <v>4000</v>
+      </c>
+      <c r="G89" t="s">
+        <v>34</v>
+      </c>
+      <c r="H89" t="s">
+        <v>54</v>
+      </c>
+      <c r="I89" t="s">
+        <v>23</v>
+      </c>
+      <c r="J89" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90">
+        <v>86</v>
+      </c>
+      <c r="B90" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D90" s="5">
+        <v>2006002</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F90">
+        <v>4000</v>
+      </c>
+      <c r="G90" t="s">
+        <v>34</v>
+      </c>
+      <c r="H90" t="s">
+        <v>54</v>
+      </c>
+      <c r="I90" t="s">
+        <v>23</v>
+      </c>
+      <c r="J90" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91">
+        <v>87</v>
+      </c>
+      <c r="B91" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D91" s="5">
+        <v>2006003</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F91">
+        <v>4000</v>
+      </c>
+      <c r="G91" t="s">
+        <v>34</v>
+      </c>
+      <c r="H91" t="s">
+        <v>54</v>
+      </c>
+      <c r="I91" t="s">
+        <v>23</v>
+      </c>
+      <c r="J91" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92">
+        <v>88</v>
+      </c>
+      <c r="B92" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D92" s="5">
+        <v>2006001</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F92">
+        <v>2000</v>
+      </c>
+      <c r="G92" t="s">
+        <v>36</v>
+      </c>
+      <c r="H92" t="s">
+        <v>54</v>
+      </c>
+      <c r="I92" t="s">
+        <v>23</v>
+      </c>
+      <c r="J92" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93">
+        <v>89</v>
+      </c>
+      <c r="B93" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D93" s="5">
+        <v>2006002</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F93">
+        <v>2000</v>
+      </c>
+      <c r="G93" t="s">
+        <v>36</v>
+      </c>
+      <c r="H93" t="s">
+        <v>54</v>
+      </c>
+      <c r="I93" t="s">
+        <v>23</v>
+      </c>
+      <c r="J93" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94">
+        <v>90</v>
+      </c>
+      <c r="B94" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D94" s="5">
+        <v>2006003</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F94">
+        <v>2000</v>
+      </c>
+      <c r="G94" t="s">
+        <v>36</v>
+      </c>
+      <c r="H94" t="s">
+        <v>54</v>
+      </c>
+      <c r="I94" t="s">
+        <v>23</v>
+      </c>
+      <c r="J94" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95">
+        <v>91</v>
+      </c>
+      <c r="B95" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" s="5">
+        <v>2007001</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F95">
+        <v>9000</v>
+      </c>
+      <c r="G95" t="s">
+        <v>21</v>
+      </c>
+      <c r="H95" t="s">
+        <v>58</v>
+      </c>
+      <c r="I95" t="s">
+        <v>23</v>
+      </c>
+      <c r="J95" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96">
+        <v>92</v>
+      </c>
+      <c r="B96" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D96" s="5">
+        <v>2007002</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F96">
+        <v>9000</v>
+      </c>
+      <c r="G96" t="s">
+        <v>21</v>
+      </c>
+      <c r="H96" t="s">
+        <v>58</v>
+      </c>
+      <c r="I96" t="s">
+        <v>23</v>
+      </c>
+      <c r="J96" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97">
+        <v>93</v>
+      </c>
+      <c r="B97" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" s="5">
+        <v>2007003</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F97">
+        <v>9000</v>
+      </c>
+      <c r="G97" t="s">
+        <v>21</v>
+      </c>
+      <c r="H97" t="s">
+        <v>58</v>
+      </c>
+      <c r="I97" t="s">
+        <v>23</v>
+      </c>
+      <c r="J97" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98">
+        <v>94</v>
+      </c>
+      <c r="B98" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D98" s="5">
+        <v>2007001</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F98">
+        <v>7000</v>
+      </c>
+      <c r="G98" t="s">
+        <v>28</v>
+      </c>
+      <c r="H98" t="s">
+        <v>58</v>
+      </c>
+      <c r="I98" t="s">
+        <v>23</v>
+      </c>
+      <c r="J98" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99">
+        <v>95</v>
+      </c>
+      <c r="B99" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D99" s="5">
+        <v>2007002</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F99">
+        <v>7000</v>
+      </c>
+      <c r="G99" t="s">
+        <v>28</v>
+      </c>
+      <c r="H99" t="s">
+        <v>58</v>
+      </c>
+      <c r="I99" t="s">
+        <v>23</v>
+      </c>
+      <c r="J99" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100">
+        <v>96</v>
+      </c>
+      <c r="B100" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D100" s="5">
+        <v>2007003</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F100">
+        <v>7000</v>
+      </c>
+      <c r="G100" t="s">
+        <v>28</v>
+      </c>
+      <c r="H100" t="s">
+        <v>58</v>
+      </c>
+      <c r="I100" t="s">
+        <v>23</v>
+      </c>
+      <c r="J100" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101">
+        <v>97</v>
+      </c>
+      <c r="B101" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D101" s="5">
+        <v>2007001</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F101">
+        <v>5000</v>
+      </c>
+      <c r="G101" t="s">
+        <v>31</v>
+      </c>
+      <c r="H101" t="s">
+        <v>58</v>
+      </c>
+      <c r="I101" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102">
+        <v>98</v>
+      </c>
+      <c r="B102" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D102" s="5">
+        <v>2007002</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F102">
+        <v>5000</v>
+      </c>
+      <c r="G102" t="s">
+        <v>31</v>
+      </c>
+      <c r="H102" t="s">
+        <v>58</v>
+      </c>
+      <c r="I102" t="s">
+        <v>23</v>
+      </c>
+      <c r="J102" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103">
+        <v>99</v>
+      </c>
+      <c r="B103" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D103" s="5">
+        <v>2007003</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F103">
+        <v>5000</v>
+      </c>
+      <c r="G103" t="s">
+        <v>31</v>
+      </c>
+      <c r="H103" t="s">
+        <v>58</v>
+      </c>
+      <c r="I103" t="s">
+        <v>23</v>
+      </c>
+      <c r="J103" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104">
+        <v>100</v>
+      </c>
+      <c r="B104" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D104" s="5">
+        <v>2007001</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F104">
+        <v>4000</v>
+      </c>
+      <c r="G104" t="s">
+        <v>34</v>
+      </c>
+      <c r="H104" t="s">
+        <v>58</v>
+      </c>
+      <c r="I104" t="s">
+        <v>23</v>
+      </c>
+      <c r="J104" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105">
+        <v>101</v>
+      </c>
+      <c r="B105" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D105" s="5">
+        <v>2007002</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F105">
+        <v>4000</v>
+      </c>
+      <c r="G105" t="s">
+        <v>34</v>
+      </c>
+      <c r="H105" t="s">
+        <v>58</v>
+      </c>
+      <c r="I105" t="s">
+        <v>23</v>
+      </c>
+      <c r="J105" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106">
+        <v>102</v>
+      </c>
+      <c r="B106" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D106" s="5">
+        <v>2007003</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F106">
+        <v>4000</v>
+      </c>
+      <c r="G106" t="s">
+        <v>34</v>
+      </c>
+      <c r="H106" t="s">
+        <v>58</v>
+      </c>
+      <c r="I106" t="s">
+        <v>23</v>
+      </c>
+      <c r="J106" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107">
+        <v>103</v>
+      </c>
+      <c r="B107" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D107" s="5">
+        <v>2007001</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F107">
+        <v>2000</v>
+      </c>
+      <c r="G107" t="s">
+        <v>36</v>
+      </c>
+      <c r="H107" t="s">
+        <v>58</v>
+      </c>
+      <c r="I107" t="s">
+        <v>23</v>
+      </c>
+      <c r="J107" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108">
+        <v>104</v>
+      </c>
+      <c r="B108" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D108" s="5">
+        <v>2007002</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F108">
+        <v>2000</v>
+      </c>
+      <c r="G108" t="s">
+        <v>36</v>
+      </c>
+      <c r="H108" t="s">
+        <v>58</v>
+      </c>
+      <c r="I108" t="s">
+        <v>23</v>
+      </c>
+      <c r="J108" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109">
+        <v>105</v>
+      </c>
+      <c r="B109" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D109" s="5">
+        <v>2007003</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F109">
+        <v>2000</v>
+      </c>
+      <c r="G109" t="s">
+        <v>36</v>
+      </c>
+      <c r="H109" t="s">
+        <v>58</v>
+      </c>
+      <c r="I109" t="s">
+        <v>23</v>
+      </c>
+      <c r="J109" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110">
+        <v>106</v>
+      </c>
+      <c r="B110" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D110" s="5">
+        <v>2008001</v>
+      </c>
+      <c r="E110" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F110">
+        <v>9000</v>
+      </c>
+      <c r="G110" t="s">
+        <v>21</v>
+      </c>
+      <c r="H110" t="s">
+        <v>62</v>
+      </c>
+      <c r="I110" t="s">
+        <v>23</v>
+      </c>
+      <c r="J110" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111">
+        <v>107</v>
+      </c>
+      <c r="B111" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D111" s="5">
+        <v>2008002</v>
+      </c>
+      <c r="E111" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F111">
+        <v>9000</v>
+      </c>
+      <c r="G111" t="s">
+        <v>21</v>
+      </c>
+      <c r="H111" t="s">
+        <v>62</v>
+      </c>
+      <c r="I111" t="s">
+        <v>23</v>
+      </c>
+      <c r="J111" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112">
+        <v>108</v>
+      </c>
+      <c r="B112" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D112" s="5">
+        <v>2008003</v>
+      </c>
+      <c r="E112" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F112">
+        <v>9000</v>
+      </c>
+      <c r="G112" t="s">
+        <v>21</v>
+      </c>
+      <c r="H112" t="s">
+        <v>62</v>
+      </c>
+      <c r="I112" t="s">
+        <v>23</v>
+      </c>
+      <c r="J112" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113">
+        <v>109</v>
+      </c>
+      <c r="B113" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D113" s="5">
+        <v>2008001</v>
+      </c>
+      <c r="E113" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F113">
+        <v>7000</v>
+      </c>
+      <c r="G113" t="s">
+        <v>28</v>
+      </c>
+      <c r="H113" t="s">
+        <v>62</v>
+      </c>
+      <c r="I113" t="s">
+        <v>23</v>
+      </c>
+      <c r="J113" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114">
+        <v>110</v>
+      </c>
+      <c r="B114" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D114" s="5">
+        <v>2008002</v>
+      </c>
+      <c r="E114" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F114">
+        <v>7000</v>
+      </c>
+      <c r="G114" t="s">
+        <v>28</v>
+      </c>
+      <c r="H114" t="s">
+        <v>62</v>
+      </c>
+      <c r="I114" t="s">
+        <v>23</v>
+      </c>
+      <c r="J114" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115">
+        <v>111</v>
+      </c>
+      <c r="B115" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D115" s="5">
+        <v>2008003</v>
+      </c>
+      <c r="E115" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F115">
+        <v>7000</v>
+      </c>
+      <c r="G115" t="s">
+        <v>28</v>
+      </c>
+      <c r="H115" t="s">
+        <v>62</v>
+      </c>
+      <c r="I115" t="s">
+        <v>23</v>
+      </c>
+      <c r="J115" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116">
+        <v>112</v>
+      </c>
+      <c r="B116" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D116" s="5">
+        <v>2008001</v>
+      </c>
+      <c r="E116" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F116">
+        <v>5000</v>
+      </c>
+      <c r="G116" t="s">
+        <v>31</v>
+      </c>
+      <c r="H116" t="s">
+        <v>62</v>
+      </c>
+      <c r="I116" t="s">
+        <v>23</v>
+      </c>
+      <c r="J116" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117">
+        <v>113</v>
+      </c>
+      <c r="B117" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D117" s="5">
+        <v>2008002</v>
+      </c>
+      <c r="E117" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F117">
+        <v>5000</v>
+      </c>
+      <c r="G117" t="s">
+        <v>31</v>
+      </c>
+      <c r="H117" t="s">
+        <v>62</v>
+      </c>
+      <c r="I117" t="s">
+        <v>23</v>
+      </c>
+      <c r="J117" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118">
+        <v>114</v>
+      </c>
+      <c r="B118" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D118" s="5">
+        <v>2008003</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F118">
+        <v>5000</v>
+      </c>
+      <c r="G118" t="s">
+        <v>31</v>
+      </c>
+      <c r="H118" t="s">
+        <v>62</v>
+      </c>
+      <c r="I118" t="s">
+        <v>23</v>
+      </c>
+      <c r="J118" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119">
+        <v>115</v>
+      </c>
+      <c r="B119" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D119" s="5">
+        <v>2008001</v>
+      </c>
+      <c r="E119" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F119">
+        <v>4000</v>
+      </c>
+      <c r="G119" t="s">
+        <v>34</v>
+      </c>
+      <c r="H119" t="s">
+        <v>62</v>
+      </c>
+      <c r="I119" t="s">
+        <v>23</v>
+      </c>
+      <c r="J119" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120">
+        <v>116</v>
+      </c>
+      <c r="B120" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D120" s="5">
+        <v>2008002</v>
+      </c>
+      <c r="E120" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F120">
+        <v>4000</v>
+      </c>
+      <c r="G120" t="s">
+        <v>34</v>
+      </c>
+      <c r="H120" t="s">
+        <v>62</v>
+      </c>
+      <c r="I120" t="s">
+        <v>23</v>
+      </c>
+      <c r="J120" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121">
+        <v>117</v>
+      </c>
+      <c r="B121" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D121" s="5">
+        <v>2008003</v>
+      </c>
+      <c r="E121" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F121">
+        <v>4000</v>
+      </c>
+      <c r="G121" t="s">
+        <v>34</v>
+      </c>
+      <c r="H121" t="s">
+        <v>62</v>
+      </c>
+      <c r="I121" t="s">
+        <v>23</v>
+      </c>
+      <c r="J121" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122">
+        <v>118</v>
+      </c>
+      <c r="B122" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D122" s="5">
+        <v>2008001</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F122">
+        <v>2000</v>
+      </c>
+      <c r="G122" t="s">
+        <v>36</v>
+      </c>
+      <c r="H122" t="s">
+        <v>62</v>
+      </c>
+      <c r="I122" t="s">
+        <v>23</v>
+      </c>
+      <c r="J122" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123">
+        <v>119</v>
+      </c>
+      <c r="B123" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D123" s="5">
+        <v>2008002</v>
+      </c>
+      <c r="E123" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F123">
+        <v>2000</v>
+      </c>
+      <c r="G123" t="s">
+        <v>36</v>
+      </c>
+      <c r="H123" t="s">
+        <v>62</v>
+      </c>
+      <c r="I123" t="s">
+        <v>23</v>
+      </c>
+      <c r="J123" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124">
+        <v>120</v>
+      </c>
+      <c r="B124" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D124" s="5">
+        <v>2008003</v>
+      </c>
+      <c r="E124" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F124">
+        <v>2000</v>
+      </c>
+      <c r="G124" t="s">
+        <v>36</v>
+      </c>
+      <c r="H124" t="s">
+        <v>62</v>
+      </c>
+      <c r="I124" t="s">
+        <v>23</v>
+      </c>
+      <c r="J124" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125">
+        <v>121</v>
+      </c>
+      <c r="B125" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D125" s="5">
+        <v>2009001</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F125">
+        <v>9000</v>
+      </c>
+      <c r="G125" t="s">
+        <v>21</v>
+      </c>
+      <c r="H125" t="s">
+        <v>66</v>
+      </c>
+      <c r="I125" t="s">
+        <v>23</v>
+      </c>
+      <c r="J125" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126">
+        <v>122</v>
+      </c>
+      <c r="B126" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D126" s="5">
+        <v>2009002</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F126">
+        <v>9000</v>
+      </c>
+      <c r="G126" t="s">
+        <v>21</v>
+      </c>
+      <c r="H126" t="s">
+        <v>66</v>
+      </c>
+      <c r="I126" t="s">
+        <v>23</v>
+      </c>
+      <c r="J126" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127">
+        <v>123</v>
+      </c>
+      <c r="B127" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D127" s="5">
+        <v>2009003</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F127">
+        <v>9000</v>
+      </c>
+      <c r="G127" t="s">
+        <v>21</v>
+      </c>
+      <c r="H127" t="s">
+        <v>66</v>
+      </c>
+      <c r="I127" t="s">
+        <v>23</v>
+      </c>
+      <c r="J127" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128">
+        <v>124</v>
+      </c>
+      <c r="B128" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D128" s="5">
+        <v>2009001</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F128">
+        <v>7000</v>
+      </c>
+      <c r="G128" t="s">
+        <v>28</v>
+      </c>
+      <c r="H128" t="s">
+        <v>66</v>
+      </c>
+      <c r="I128" t="s">
+        <v>23</v>
+      </c>
+      <c r="J128" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129">
+        <v>125</v>
+      </c>
+      <c r="B129" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D129" s="5">
+        <v>2009002</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F129">
+        <v>7000</v>
+      </c>
+      <c r="G129" t="s">
+        <v>28</v>
+      </c>
+      <c r="H129" t="s">
+        <v>66</v>
+      </c>
+      <c r="I129" t="s">
+        <v>23</v>
+      </c>
+      <c r="J129" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130">
+        <v>126</v>
+      </c>
+      <c r="B130" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D130" s="5">
+        <v>2009003</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F130">
+        <v>7000</v>
+      </c>
+      <c r="G130" t="s">
+        <v>28</v>
+      </c>
+      <c r="H130" t="s">
+        <v>66</v>
+      </c>
+      <c r="I130" t="s">
+        <v>23</v>
+      </c>
+      <c r="J130" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131">
+        <v>127</v>
+      </c>
+      <c r="B131" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D131" s="5">
+        <v>2009001</v>
+      </c>
+      <c r="E131" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F131">
+        <v>5000</v>
+      </c>
+      <c r="G131" t="s">
+        <v>31</v>
+      </c>
+      <c r="H131" t="s">
+        <v>66</v>
+      </c>
+      <c r="I131" t="s">
+        <v>23</v>
+      </c>
+      <c r="J131" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132">
+        <v>128</v>
+      </c>
+      <c r="B132" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D132" s="5">
+        <v>2009002</v>
+      </c>
+      <c r="E132" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F132">
+        <v>5000</v>
+      </c>
+      <c r="G132" t="s">
+        <v>31</v>
+      </c>
+      <c r="H132" t="s">
+        <v>66</v>
+      </c>
+      <c r="I132" t="s">
+        <v>23</v>
+      </c>
+      <c r="J132" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133">
+        <v>129</v>
+      </c>
+      <c r="B133" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D133" s="5">
+        <v>2009003</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F133">
+        <v>5000</v>
+      </c>
+      <c r="G133" t="s">
+        <v>31</v>
+      </c>
+      <c r="H133" t="s">
+        <v>66</v>
+      </c>
+      <c r="I133" t="s">
+        <v>23</v>
+      </c>
+      <c r="J133" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134">
+        <v>130</v>
+      </c>
+      <c r="B134" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D134" s="5">
+        <v>2009001</v>
+      </c>
+      <c r="E134" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F134">
+        <v>4000</v>
+      </c>
+      <c r="G134" t="s">
+        <v>34</v>
+      </c>
+      <c r="H134" t="s">
+        <v>66</v>
+      </c>
+      <c r="I134" t="s">
+        <v>23</v>
+      </c>
+      <c r="J134" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135">
+        <v>131</v>
+      </c>
+      <c r="B135" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D135" s="5">
+        <v>2009002</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F135">
+        <v>4000</v>
+      </c>
+      <c r="G135" t="s">
+        <v>34</v>
+      </c>
+      <c r="H135" t="s">
+        <v>66</v>
+      </c>
+      <c r="I135" t="s">
+        <v>23</v>
+      </c>
+      <c r="J135" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136">
+        <v>132</v>
+      </c>
+      <c r="B136" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D136" s="5">
+        <v>2009003</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F136">
+        <v>4000</v>
+      </c>
+      <c r="G136" t="s">
+        <v>34</v>
+      </c>
+      <c r="H136" t="s">
+        <v>66</v>
+      </c>
+      <c r="I136" t="s">
+        <v>23</v>
+      </c>
+      <c r="J136" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137">
+        <v>133</v>
+      </c>
+      <c r="B137" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D137" s="5">
+        <v>2009001</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F137">
+        <v>2000</v>
+      </c>
+      <c r="G137" t="s">
+        <v>36</v>
+      </c>
+      <c r="H137" t="s">
+        <v>66</v>
+      </c>
+      <c r="I137" t="s">
+        <v>23</v>
+      </c>
+      <c r="J137" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138">
+        <v>134</v>
+      </c>
+      <c r="B138" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D138" s="5">
+        <v>2009002</v>
+      </c>
+      <c r="E138" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F138">
+        <v>2000</v>
+      </c>
+      <c r="G138" t="s">
+        <v>36</v>
+      </c>
+      <c r="H138" t="s">
+        <v>66</v>
+      </c>
+      <c r="I138" t="s">
+        <v>23</v>
+      </c>
+      <c r="J138" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139">
+        <v>135</v>
+      </c>
+      <c r="B139" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D139" s="5">
+        <v>2009003</v>
+      </c>
+      <c r="E139" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F139">
+        <v>2000</v>
+      </c>
+      <c r="G139" t="s">
+        <v>36</v>
+      </c>
+      <c r="H139" t="s">
+        <v>66</v>
+      </c>
+      <c r="I139" t="s">
+        <v>23</v>
+      </c>
+      <c r="J139" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
